--- a/CASES/Insitu XRD/intensity.xlsx
+++ b/CASES/Insitu XRD/intensity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\博士\NCM\苏蔚测的原位XRD\241009-huangyu-bare 811 710\bare 811 710 insitu XRD csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA96E30B-8C4E-44AE-9C23-326EE57C2E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7A9961-A505-47D9-93F2-B86A7746BD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="31420" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -347,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
@@ -358,7 +358,7 @@
         <v>10.094481699999999</v>
       </c>
       <c r="B1" s="1">
-        <v>6039</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -366,7 +366,7 @@
         <v>10.252045091999999</v>
       </c>
       <c r="B2" s="1">
-        <v>5878</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -374,7 +374,7 @@
         <v>10.409608484</v>
       </c>
       <c r="B3" s="1">
-        <v>5737</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -382,7 +382,7 @@
         <v>10.567171876</v>
       </c>
       <c r="B4" s="1">
-        <v>5561</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -390,7 +390,7 @@
         <v>10.724735268</v>
       </c>
       <c r="B5" s="1">
-        <v>5506</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -398,7 +398,7 @@
         <v>10.882298661</v>
       </c>
       <c r="B6" s="1">
-        <v>5295</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -406,7 +406,7 @@
         <v>11.039862053</v>
       </c>
       <c r="B7" s="1">
-        <v>5066</v>
+        <v>5225</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -414,7 +414,7 @@
         <v>11.197425445</v>
       </c>
       <c r="B8" s="1">
-        <v>5088</v>
+        <v>5048</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -422,7 +422,7 @@
         <v>11.354988837000001</v>
       </c>
       <c r="B9" s="1">
-        <v>4783</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -430,7 +430,7 @@
         <v>11.512552229000001</v>
       </c>
       <c r="B10" s="1">
-        <v>4736</v>
+        <v>4844</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -438,7 +438,7 @@
         <v>11.670115621000001</v>
       </c>
       <c r="B11" s="1">
-        <v>4667</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -446,7 +446,7 @@
         <v>11.827679012999999</v>
       </c>
       <c r="B12" s="1">
-        <v>4500</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -454,7 +454,7 @@
         <v>11.985242404999999</v>
       </c>
       <c r="B13" s="1">
-        <v>4399</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -462,15 +462,15 @@
         <v>12.142805796999999</v>
       </c>
       <c r="B14" s="1">
-        <v>4240</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>12.30036919</v>
+        <v>12.300369189</v>
       </c>
       <c r="B15" s="1">
-        <v>4268</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -478,7 +478,7 @@
         <v>12.457932582</v>
       </c>
       <c r="B16" s="1">
-        <v>4243</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -486,7 +486,7 @@
         <v>12.615495974</v>
       </c>
       <c r="B17" s="1">
-        <v>4029</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -494,7 +494,7 @@
         <v>12.773059366</v>
       </c>
       <c r="B18" s="1">
-        <v>4052</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -502,7 +502,7 @@
         <v>12.930622758</v>
       </c>
       <c r="B19" s="1">
-        <v>3949</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -510,7 +510,7 @@
         <v>13.08818615</v>
       </c>
       <c r="B20" s="1">
-        <v>3878</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -518,7 +518,7 @@
         <v>13.245749542</v>
       </c>
       <c r="B21" s="1">
-        <v>3924</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -526,7 +526,7 @@
         <v>13.403312934000001</v>
       </c>
       <c r="B22" s="1">
-        <v>3777</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -534,23 +534,23 @@
         <v>13.560876326000001</v>
       </c>
       <c r="B23" s="1">
-        <v>3742</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>13.718439718999999</v>
+        <v>13.718439718000001</v>
       </c>
       <c r="B24" s="1">
-        <v>3687</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>13.876003110999999</v>
+        <v>13.876003109999999</v>
       </c>
       <c r="B25" s="1">
-        <v>3611</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -558,7 +558,7 @@
         <v>14.033566502999999</v>
       </c>
       <c r="B26" s="1">
-        <v>3522</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -566,7 +566,7 @@
         <v>14.191129895</v>
       </c>
       <c r="B27" s="1">
-        <v>3532</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -574,7 +574,7 @@
         <v>14.348693287</v>
       </c>
       <c r="B28" s="1">
-        <v>3464</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -582,7 +582,7 @@
         <v>14.506256679</v>
       </c>
       <c r="B29" s="1">
-        <v>3301</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -590,7 +590,7 @@
         <v>14.663820071</v>
       </c>
       <c r="B30" s="1">
-        <v>3295</v>
+        <v>3327</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -598,7 +598,7 @@
         <v>14.821383463</v>
       </c>
       <c r="B31" s="1">
-        <v>3337</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -606,23 +606,23 @@
         <v>14.978946855</v>
       </c>
       <c r="B32" s="1">
-        <v>3244</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>15.136510248</v>
+        <v>15.136510247</v>
       </c>
       <c r="B33" s="1">
-        <v>3230</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>15.294073640000001</v>
+        <v>15.294073639</v>
       </c>
       <c r="B34" s="1">
-        <v>3107</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
         <v>15.451637032000001</v>
       </c>
       <c r="B35" s="1">
-        <v>3197</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -638,7 +638,7 @@
         <v>15.609200424000001</v>
       </c>
       <c r="B36" s="1">
-        <v>3195</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -646,7 +646,7 @@
         <v>15.766763815999999</v>
       </c>
       <c r="B37" s="1">
-        <v>3062</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -654,7 +654,7 @@
         <v>15.924327207999999</v>
       </c>
       <c r="B38" s="1">
-        <v>3068</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -662,7 +662,7 @@
         <v>16.081890600000001</v>
       </c>
       <c r="B39" s="1">
-        <v>3076</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -670,7 +670,7 @@
         <v>16.239453992000001</v>
       </c>
       <c r="B40" s="1">
-        <v>3006</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -678,31 +678,31 @@
         <v>16.397017384000002</v>
       </c>
       <c r="B41" s="1">
-        <v>2973</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>16.554580777000002</v>
+        <v>16.554580776000002</v>
       </c>
       <c r="B42" s="1">
-        <v>2949</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>16.712144168999998</v>
+        <v>16.712144167999998</v>
       </c>
       <c r="B43" s="1">
-        <v>3022</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>16.869707560999998</v>
+        <v>16.869707559999998</v>
       </c>
       <c r="B44" s="1">
-        <v>2958</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -710,7 +710,7 @@
         <v>17.027270952999999</v>
       </c>
       <c r="B45" s="1">
-        <v>2819</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -726,7 +726,7 @@
         <v>17.342397736999999</v>
       </c>
       <c r="B47" s="1">
-        <v>2841</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -734,7 +734,7 @@
         <v>17.499961128999999</v>
       </c>
       <c r="B48" s="1">
-        <v>2852</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -742,7 +742,7 @@
         <v>17.657524520999999</v>
       </c>
       <c r="B49" s="1">
-        <v>2851</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -750,39 +750,39 @@
         <v>17.815087912999999</v>
       </c>
       <c r="B50" s="1">
-        <v>2837</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>17.972651305999999</v>
+        <v>17.972651304999999</v>
       </c>
       <c r="B51" s="1">
-        <v>2844</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>18.130214698</v>
+        <v>18.130214697</v>
       </c>
       <c r="B52" s="1">
-        <v>2866</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>18.28777809</v>
+        <v>18.287778089</v>
       </c>
       <c r="B53" s="1">
-        <v>2838</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>18.445341482</v>
+        <v>18.445341481</v>
       </c>
       <c r="B54" s="1">
-        <v>3088</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>18.602904874</v>
       </c>
       <c r="B55" s="1">
-        <v>3366</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -798,7 +798,7 @@
         <v>18.760468266</v>
       </c>
       <c r="B56" s="1">
-        <v>5296</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
         <v>18.918031658</v>
       </c>
       <c r="B57" s="1">
-        <v>6594</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -814,7 +814,7 @@
         <v>19.07559505</v>
       </c>
       <c r="B58" s="1">
-        <v>3565</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,39 +822,39 @@
         <v>19.233158442000001</v>
       </c>
       <c r="B59" s="1">
-        <v>3074</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>19.390721835000001</v>
+        <v>19.390721834000001</v>
       </c>
       <c r="B60" s="1">
-        <v>2959</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>19.548285227000001</v>
+        <v>19.548285226000001</v>
       </c>
       <c r="B61" s="1">
-        <v>2777</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>19.705848619000001</v>
+        <v>19.705848618000001</v>
       </c>
       <c r="B62" s="1">
-        <v>2930</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>19.863412011000001</v>
+        <v>19.863412010000001</v>
       </c>
       <c r="B63" s="1">
-        <v>2748</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -862,7 +862,7 @@
         <v>20.020975403000001</v>
       </c>
       <c r="B64" s="1">
-        <v>2907</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -870,7 +870,7 @@
         <v>20.178538795000001</v>
       </c>
       <c r="B65" s="1">
-        <v>2778</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -878,7 +878,7 @@
         <v>20.336102187000002</v>
       </c>
       <c r="B66" s="1">
-        <v>2775</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -886,7 +886,7 @@
         <v>20.493665579000002</v>
       </c>
       <c r="B67" s="1">
-        <v>2745</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -894,47 +894,47 @@
         <v>20.651228970999998</v>
       </c>
       <c r="B68" s="1">
-        <v>2882</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>20.808792363999999</v>
+        <v>20.808792362999998</v>
       </c>
       <c r="B69" s="1">
-        <v>2825</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>20.966355755999999</v>
+        <v>20.966355754999999</v>
       </c>
       <c r="B70" s="1">
-        <v>2831</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>21.123919147999999</v>
+        <v>21.123919146999999</v>
       </c>
       <c r="B71" s="1">
-        <v>2876</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>21.281482539999999</v>
+        <v>21.281482538999999</v>
       </c>
       <c r="B72" s="1">
-        <v>2807</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>21.439045931999999</v>
+        <v>21.439045930999999</v>
       </c>
       <c r="B73" s="1">
-        <v>2804</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
         <v>21.596609323999999</v>
       </c>
       <c r="B74" s="1">
-        <v>2918</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -950,7 +950,7 @@
         <v>21.754172715999999</v>
       </c>
       <c r="B75" s="1">
-        <v>2846</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -958,7 +958,7 @@
         <v>21.911736107999999</v>
       </c>
       <c r="B76" s="1">
-        <v>2857</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -966,47 +966,47 @@
         <v>22.0692995</v>
       </c>
       <c r="B77" s="1">
-        <v>2933</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>22.226862893</v>
+        <v>22.226862892</v>
       </c>
       <c r="B78" s="1">
-        <v>2899</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>22.384426285</v>
+        <v>22.384426284</v>
       </c>
       <c r="B79" s="1">
-        <v>2987</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>22.541989677</v>
+        <v>22.541989676</v>
       </c>
       <c r="B80" s="1">
-        <v>2998</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>22.699553069</v>
+        <v>22.699553068</v>
       </c>
       <c r="B81" s="1">
-        <v>3102</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>22.857116461</v>
+        <v>22.85711646</v>
       </c>
       <c r="B82" s="1">
-        <v>2941</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1014,7 +1014,7 @@
         <v>23.014679853000001</v>
       </c>
       <c r="B83" s="1">
-        <v>2769</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1022,7 +1022,7 @@
         <v>23.172243245000001</v>
       </c>
       <c r="B84" s="1">
-        <v>2892</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1030,7 +1030,7 @@
         <v>23.329806637000001</v>
       </c>
       <c r="B85" s="1">
-        <v>2836</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1038,55 +1038,55 @@
         <v>23.487370029000001</v>
       </c>
       <c r="B86" s="1">
-        <v>2800</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>23.644933422000001</v>
+        <v>23.644933421000001</v>
       </c>
       <c r="B87" s="1">
-        <v>2850</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>23.802496814000001</v>
+        <v>23.802496813000001</v>
       </c>
       <c r="B88" s="1">
-        <v>2661</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>23.960060206000001</v>
+        <v>23.960060205000001</v>
       </c>
       <c r="B89" s="1">
-        <v>2685</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>24.117623598000002</v>
+        <v>24.117623597000001</v>
       </c>
       <c r="B90" s="1">
-        <v>2748</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>24.275186990000002</v>
+        <v>24.275186989000002</v>
       </c>
       <c r="B91" s="1">
-        <v>3125</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>24.432750381999998</v>
+        <v>24.432750381000002</v>
       </c>
       <c r="B92" s="1">
-        <v>3198</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1094,7 +1094,7 @@
         <v>24.590313773999998</v>
       </c>
       <c r="B93" s="1">
-        <v>2715</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1102,7 +1102,7 @@
         <v>24.747877165999999</v>
       </c>
       <c r="B94" s="1">
-        <v>2709</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1110,63 +1110,63 @@
         <v>24.905440557999999</v>
       </c>
       <c r="B95" s="1">
-        <v>2660</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <v>25.063003950999999</v>
+        <v>25.063003949999999</v>
       </c>
       <c r="B96" s="1">
-        <v>2615</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <v>25.220567342999999</v>
+        <v>25.220567341999999</v>
       </c>
       <c r="B97" s="1">
-        <v>2592</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>25.378130734999999</v>
+        <v>25.378130733999999</v>
       </c>
       <c r="B98" s="1">
-        <v>2628</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>25.535694126999999</v>
+        <v>25.535694125999999</v>
       </c>
       <c r="B99" s="1">
-        <v>2539</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>25.693257518999999</v>
+        <v>25.693257517999999</v>
       </c>
       <c r="B100" s="1">
-        <v>2493</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>25.850820911</v>
+        <v>25.850820909999999</v>
       </c>
       <c r="B101" s="1">
-        <v>2611</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>26.008384303</v>
+        <v>26.008384302</v>
       </c>
       <c r="B102" s="1">
-        <v>2618</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -1174,7 +1174,7 @@
         <v>26.165947695</v>
       </c>
       <c r="B103" s="1">
-        <v>2522</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -1182,63 +1182,63 @@
         <v>26.323511087</v>
       </c>
       <c r="B104" s="1">
-        <v>2610</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>26.48107448</v>
+        <v>26.481074479</v>
       </c>
       <c r="B105" s="1">
-        <v>2493</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <v>26.638637872</v>
+        <v>26.638637871</v>
       </c>
       <c r="B106" s="1">
-        <v>2563</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>26.796201264</v>
+        <v>26.796201263</v>
       </c>
       <c r="B107" s="1">
-        <v>2532</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>26.953764656000001</v>
+        <v>26.953764655000001</v>
       </c>
       <c r="B108" s="1">
-        <v>2490</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>27.111328048000001</v>
+        <v>27.111328047000001</v>
       </c>
       <c r="B109" s="1">
-        <v>2557</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>27.268891440000001</v>
+        <v>27.268891439000001</v>
       </c>
       <c r="B110" s="1">
-        <v>2482</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>27.426454832000001</v>
+        <v>27.426454831000001</v>
       </c>
       <c r="B111" s="1">
-        <v>2396</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1246,7 +1246,7 @@
         <v>27.584018224000001</v>
       </c>
       <c r="B112" s="1">
-        <v>2552</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -1254,28 +1254,28 @@
         <v>27.741581616000001</v>
       </c>
       <c r="B113" s="1">
-        <v>2495</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>27.899145009000001</v>
+        <v>27.899145008000001</v>
       </c>
       <c r="B114" s="1">
-        <v>2539</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>28.056708401000002</v>
+        <v>28.056708400000002</v>
       </c>
       <c r="B115" s="1">
-        <v>2491</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>28.214271793000002</v>
+        <v>28.214271792000002</v>
       </c>
       <c r="B116" s="1">
         <v>2487</v>
@@ -1283,42 +1283,42 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>28.371835184999998</v>
+        <v>28.371835183999998</v>
       </c>
       <c r="B117" s="1">
-        <v>2497</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>28.529398576999998</v>
+        <v>28.529398575999998</v>
       </c>
       <c r="B118" s="1">
-        <v>2423</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>28.686961968999999</v>
+        <v>28.686961967999999</v>
       </c>
       <c r="B119" s="1">
-        <v>2465</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>28.844525360999999</v>
+        <v>28.844525359999999</v>
       </c>
       <c r="B120" s="1">
-        <v>2453</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>29.002088752999999</v>
+        <v>29.002088751999999</v>
       </c>
       <c r="B121" s="1">
-        <v>2576</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -1326,252 +1326,252 @@
         <v>29.159652144999999</v>
       </c>
       <c r="B122" s="1">
-        <v>2449</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>29.317215537999999</v>
+        <v>29.317215536999999</v>
       </c>
       <c r="B123" s="1">
-        <v>2459</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>29.474778929999999</v>
+        <v>29.474778928999999</v>
       </c>
       <c r="B124" s="1">
-        <v>2429</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>29.632342322</v>
+        <v>29.632342320999999</v>
       </c>
       <c r="B125" s="1">
-        <v>2535</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>29.789905714</v>
+        <v>29.789905713</v>
       </c>
       <c r="B126" s="1">
-        <v>2477</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>29.947469106</v>
+        <v>29.947469105</v>
       </c>
       <c r="B127" s="1">
-        <v>2586</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>30.105032498</v>
+        <v>30.105032497</v>
       </c>
       <c r="B128" s="1">
-        <v>2565</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>30.26259589</v>
+        <v>30.262595889</v>
       </c>
       <c r="B129" s="1">
-        <v>2408</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>30.420159282</v>
+        <v>30.420159281</v>
       </c>
       <c r="B130" s="1">
-        <v>2521</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>30.577722675</v>
+        <v>30.577722673</v>
       </c>
       <c r="B131" s="1">
-        <v>2453</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
-        <v>30.735286067000001</v>
+        <v>30.735286066</v>
       </c>
       <c r="B132" s="1">
-        <v>2525</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
-        <v>30.892849459000001</v>
+        <v>30.892849458000001</v>
       </c>
       <c r="B133" s="1">
-        <v>2557</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>31.050412851000001</v>
+        <v>31.050412850000001</v>
       </c>
       <c r="B134" s="1">
-        <v>2520</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>31.207976243000001</v>
+        <v>31.207976242000001</v>
       </c>
       <c r="B135" s="1">
-        <v>2522</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>31.365539635000001</v>
+        <v>31.365539634000001</v>
       </c>
       <c r="B136" s="1">
-        <v>2489</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>31.523103027000001</v>
+        <v>31.523103026000001</v>
       </c>
       <c r="B137" s="1">
-        <v>2515</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
-        <v>31.680666419000001</v>
+        <v>31.680666418000001</v>
       </c>
       <c r="B138" s="1">
-        <v>2551</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
-        <v>31.838229811000001</v>
+        <v>31.838229810000001</v>
       </c>
       <c r="B139" s="1">
-        <v>2549</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
-        <v>31.995793204000002</v>
+        <v>31.995793202000002</v>
       </c>
       <c r="B140" s="1">
-        <v>2579</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>32.153356596000002</v>
+        <v>32.153356594999998</v>
       </c>
       <c r="B141" s="1">
-        <v>2574</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>32.310919988000002</v>
+        <v>32.310919986999998</v>
       </c>
       <c r="B142" s="1">
-        <v>2578</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>32.468483380000002</v>
+        <v>32.468483378999998</v>
       </c>
       <c r="B143" s="1">
-        <v>2474</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>32.626046772000002</v>
+        <v>32.626046770999999</v>
       </c>
       <c r="B144" s="1">
-        <v>2570</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>32.783610164000002</v>
+        <v>32.783610162999999</v>
       </c>
       <c r="B145" s="1">
-        <v>2407</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>32.941173556000003</v>
+        <v>32.941173554999999</v>
       </c>
       <c r="B146" s="1">
-        <v>2600</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>33.098736948000003</v>
+        <v>33.098736946999999</v>
       </c>
       <c r="B147" s="1">
-        <v>2429</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>33.256300340000003</v>
+        <v>33.256300338999999</v>
       </c>
       <c r="B148" s="1">
-        <v>2679</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>33.413863732999999</v>
+        <v>33.413863730999999</v>
       </c>
       <c r="B149" s="1">
-        <v>2591</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>33.571427125</v>
+        <v>33.571427122999999</v>
       </c>
       <c r="B150" s="1">
-        <v>2567</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>33.728990517</v>
+        <v>33.728990516000003</v>
       </c>
       <c r="B151" s="1">
-        <v>2718</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>33.886553909</v>
+        <v>33.886553908000003</v>
       </c>
       <c r="B152" s="1">
-        <v>2580</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>34.044117301</v>
+        <v>34.044117300000003</v>
       </c>
       <c r="B153" s="1">
         <v>2678</v>
@@ -1579,798 +1579,1415 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>34.201680693</v>
+        <v>34.201680691999996</v>
       </c>
       <c r="B154" s="1">
-        <v>2695</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
-        <v>34.359244085</v>
+        <v>34.359244083999997</v>
       </c>
       <c r="B155" s="1">
-        <v>2730</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
-        <v>34.516807477</v>
+        <v>34.516807475999997</v>
       </c>
       <c r="B156" s="1">
-        <v>2609</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
-        <v>34.674370869000001</v>
+        <v>34.674370867999997</v>
       </c>
       <c r="B157" s="1">
-        <v>2653</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>34.831934261999997</v>
+        <v>34.831934259999997</v>
       </c>
       <c r="B158" s="1">
-        <v>2638</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>34.989497653999997</v>
+        <v>34.989497651999997</v>
       </c>
       <c r="B159" s="1">
-        <v>2710</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>35.147061045999997</v>
+        <v>35.147061043999997</v>
       </c>
       <c r="B160" s="1">
-        <v>2781</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>35.304624437999998</v>
+        <v>35.304624437000001</v>
       </c>
       <c r="B161" s="1">
-        <v>2718</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
-        <v>35.462187829999998</v>
+        <v>35.462187829000001</v>
       </c>
       <c r="B162" s="1">
-        <v>2808</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>35.619751221999998</v>
+        <v>35.619751221000001</v>
       </c>
       <c r="B163" s="1">
-        <v>2818</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
-        <v>35.777314613999998</v>
+        <v>35.777314613000001</v>
       </c>
       <c r="B164" s="1">
-        <v>2803</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
-        <v>35.934878005999998</v>
+        <v>35.934878005000002</v>
       </c>
       <c r="B165" s="1">
-        <v>2769</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
-        <v>36.092441397999998</v>
+        <v>36.092441397000002</v>
       </c>
       <c r="B166" s="1">
-        <v>2828</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>36.250004791000002</v>
+        <v>36.250004789000002</v>
       </c>
       <c r="B167" s="1">
-        <v>2956</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
-        <v>36.407568183000002</v>
+        <v>36.407568181000002</v>
       </c>
       <c r="B168" s="1">
-        <v>2990</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
-        <v>36.565131575000002</v>
+        <v>36.565131573000002</v>
       </c>
       <c r="B169" s="1">
-        <v>3238</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
-        <v>36.722694967000002</v>
+        <v>36.722694965999999</v>
       </c>
       <c r="B170" s="1">
-        <v>3918</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
-        <v>36.880258359000003</v>
+        <v>36.880258357999999</v>
       </c>
       <c r="B171" s="1">
-        <v>6817</v>
+        <v>4997</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
-        <v>37.037821751000003</v>
+        <v>37.037821749999999</v>
       </c>
       <c r="B172" s="1">
-        <v>9000</v>
+        <v>6931</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
-        <v>37.195385143000003</v>
+        <v>37.195385141999999</v>
       </c>
       <c r="B173" s="1">
-        <v>4734</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
-        <v>37.352948535000003</v>
+        <v>37.352948533999999</v>
       </c>
       <c r="B174" s="1">
-        <v>3474</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
-        <v>37.510511927000003</v>
+        <v>37.510511926</v>
       </c>
       <c r="B175" s="1">
-        <v>3236</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
-        <v>37.66807532</v>
+        <v>37.668075318</v>
       </c>
       <c r="B176" s="1">
-        <v>3141</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
-        <v>37.825638712</v>
+        <v>37.82563871</v>
       </c>
       <c r="B177" s="1">
-        <v>3179</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
-        <v>37.983202104</v>
+        <v>37.983202102</v>
       </c>
       <c r="B178" s="1">
-        <v>3526</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
-        <v>38.140765496</v>
+        <v>38.140765494</v>
       </c>
       <c r="B179" s="1">
-        <v>3764</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
-        <v>38.298328888</v>
+        <v>38.298328886999997</v>
       </c>
       <c r="B180" s="1">
-        <v>3458</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
-        <v>38.45589228</v>
+        <v>38.455892278999997</v>
       </c>
       <c r="B181" s="1">
-        <v>3992</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
-        <v>38.613455672000001</v>
+        <v>38.613455670999997</v>
       </c>
       <c r="B182" s="1">
-        <v>7770</v>
+        <v>6589</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
-        <v>38.771019064000001</v>
+        <v>38.771019062999997</v>
       </c>
       <c r="B183" s="1">
-        <v>6149</v>
+        <v>6499</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
-        <v>38.928582456000001</v>
+        <v>38.928582454999997</v>
       </c>
       <c r="B184" s="1">
-        <v>3272</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
-        <v>39.086145848999998</v>
+        <v>39.086145846999997</v>
       </c>
       <c r="B185" s="1">
-        <v>3160</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>39.243709240999998</v>
+        <v>39.243709238999998</v>
       </c>
       <c r="B186" s="1">
-        <v>2991</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>39.401272632999998</v>
+        <v>39.401272630999998</v>
       </c>
       <c r="B187" s="1">
-        <v>3116</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
-        <v>39.558836024999998</v>
+        <v>39.558836022999998</v>
       </c>
       <c r="B188" s="1">
-        <v>3131</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
-        <v>39.716399416999998</v>
+        <v>39.716399414999998</v>
       </c>
       <c r="B189" s="1">
-        <v>3087</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>39.873962808999998</v>
+        <v>39.873962808000002</v>
       </c>
       <c r="B190" s="1">
-        <v>2991</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
-        <v>40.031526200999998</v>
+        <v>40.031526200000002</v>
       </c>
       <c r="B191" s="1">
-        <v>2992</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
-        <v>40.189089592999999</v>
+        <v>40.189089592000002</v>
       </c>
       <c r="B192" s="1">
-        <v>2974</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
-        <v>40.346652984999999</v>
+        <v>40.346652984000002</v>
       </c>
       <c r="B193" s="1">
-        <v>2970</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
-        <v>40.504216378000002</v>
+        <v>40.504216376000002</v>
       </c>
       <c r="B194" s="1">
-        <v>2996</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
-        <v>40.661779770000003</v>
+        <v>40.661779768000002</v>
       </c>
       <c r="B195" s="1">
-        <v>3077</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
-        <v>40.819343162000003</v>
+        <v>40.819343160000003</v>
       </c>
       <c r="B196" s="1">
-        <v>2948</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
-        <v>40.976906554000003</v>
+        <v>40.976906552000003</v>
       </c>
       <c r="B197" s="1">
-        <v>3030</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
-        <v>41.134469946000003</v>
+        <v>41.134469944000003</v>
       </c>
       <c r="B198" s="1">
-        <v>3071</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
-        <v>41.292033338000003</v>
+        <v>41.292033336999999</v>
       </c>
       <c r="B199" s="1">
-        <v>3135</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
-        <v>41.449596730000003</v>
+        <v>41.449596729</v>
       </c>
       <c r="B200" s="1">
-        <v>3094</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
-        <v>41.607160122000003</v>
+        <v>41.607160121</v>
       </c>
       <c r="B201" s="1">
-        <v>3120</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
-        <v>41.764723514000003</v>
+        <v>41.764723513</v>
       </c>
       <c r="B202" s="1">
-        <v>3115</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
-        <v>41.922286907</v>
+        <v>41.922286905</v>
       </c>
       <c r="B203" s="1">
-        <v>3074</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
-        <v>42.079850299</v>
+        <v>42.079850297</v>
       </c>
       <c r="B204" s="1">
-        <v>3198</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
-        <v>42.237413691</v>
+        <v>42.237413689</v>
       </c>
       <c r="B205" s="1">
-        <v>3506</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
-        <v>42.394977083000001</v>
+        <v>42.394977081</v>
       </c>
       <c r="B206" s="1">
-        <v>3265</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
-        <v>42.552540475000001</v>
+        <v>42.552540473000001</v>
       </c>
       <c r="B207" s="1">
-        <v>3264</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
-        <v>42.710103867000001</v>
+        <v>42.710103865000001</v>
       </c>
       <c r="B208" s="1">
-        <v>3142</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
-        <v>42.867667259000001</v>
+        <v>42.867667257999997</v>
       </c>
       <c r="B209" s="1">
-        <v>3248</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
-        <v>43.025230651000001</v>
+        <v>43.025230649999997</v>
       </c>
       <c r="B210" s="1">
-        <v>3136</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
-        <v>43.182794043000001</v>
+        <v>43.182794041999998</v>
       </c>
       <c r="B211" s="1">
-        <v>3313</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
-        <v>43.340357435999998</v>
+        <v>43.340357433999998</v>
       </c>
       <c r="B212" s="1">
-        <v>3265</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
-        <v>43.497920827999998</v>
+        <v>43.497920825999998</v>
       </c>
       <c r="B213" s="1">
-        <v>3581</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
-        <v>43.655484219999998</v>
+        <v>43.655484217999998</v>
       </c>
       <c r="B214" s="1">
-        <v>3397</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
-        <v>43.813047611999998</v>
+        <v>43.813047609999998</v>
       </c>
       <c r="B215" s="1">
-        <v>3519</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
-        <v>43.970611003999998</v>
+        <v>43.970611001999998</v>
       </c>
       <c r="B216" s="1">
-        <v>3730</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
-        <v>44.128174395999999</v>
+        <v>44.128174393999998</v>
       </c>
       <c r="B217" s="1">
-        <v>3758</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
-        <v>44.285737787999999</v>
+        <v>44.285737785999999</v>
       </c>
       <c r="B218" s="1">
-        <v>4164</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
-        <v>44.443301179999999</v>
+        <v>44.443301179000002</v>
       </c>
       <c r="B219" s="1">
-        <v>5963</v>
+        <v>5296</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
-        <v>44.600864571999999</v>
+        <v>44.600864571000002</v>
       </c>
       <c r="B220" s="1">
-        <v>12619</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
-        <v>44.758427965000003</v>
+        <v>44.758427963000003</v>
       </c>
       <c r="B221" s="1">
-        <v>18218</v>
+        <v>16121</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
-        <v>44.915991357000003</v>
+        <v>44.915991355000003</v>
       </c>
       <c r="B222" s="1">
-        <v>12058</v>
+        <v>14649</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
-        <v>45.073554749000003</v>
+        <v>45.073554747000003</v>
       </c>
       <c r="B223" s="1">
-        <v>6198</v>
+        <v>7884</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
-        <v>45.231118141000003</v>
+        <v>45.231118139000003</v>
       </c>
       <c r="B224" s="1">
-        <v>4068</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
-        <v>45.388681533000003</v>
+        <v>45.388681531000003</v>
       </c>
       <c r="B225" s="1">
-        <v>3626</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
-        <v>45.546244925000003</v>
+        <v>45.546244923000003</v>
       </c>
       <c r="B226" s="1">
-        <v>3522</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
-        <v>45.703808316999996</v>
+        <v>45.703808315000003</v>
       </c>
       <c r="B227" s="1">
-        <v>3438</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
-        <v>45.861371708999997</v>
+        <v>45.861371708</v>
       </c>
       <c r="B228" s="1">
-        <v>3403</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
-        <v>46.018935100999997</v>
+        <v>46.0189351</v>
       </c>
       <c r="B229" s="1">
-        <v>3451</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
-        <v>46.176498494000001</v>
+        <v>46.176498492</v>
       </c>
       <c r="B230" s="1">
-        <v>3398</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
-        <v>46.334061886000001</v>
+        <v>46.334061884</v>
       </c>
       <c r="B231" s="1">
-        <v>3236</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
-        <v>46.491625278000001</v>
+        <v>46.491625276000001</v>
       </c>
       <c r="B232" s="1">
-        <v>3340</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
-        <v>46.649188670000001</v>
+        <v>46.649188668000001</v>
       </c>
       <c r="B233" s="1">
-        <v>3274</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
-        <v>46.806752062000001</v>
+        <v>46.806752060000001</v>
       </c>
       <c r="B234" s="1">
-        <v>3357</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
-        <v>46.964315454000001</v>
+        <v>46.964315452000001</v>
       </c>
       <c r="B235" s="1">
-        <v>3423</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
-        <v>47.121878846000001</v>
+        <v>47.121878844000001</v>
       </c>
       <c r="B236" s="1">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
-        <v>47.279442238000001</v>
+        <v>47.279442236000001</v>
       </c>
       <c r="B237" s="1">
-        <v>3477</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
-        <v>47.437005630000002</v>
+        <v>47.437005628999998</v>
       </c>
       <c r="B238" s="1">
-        <v>3388</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
-        <v>47.594569022999998</v>
+        <v>47.594569020999998</v>
       </c>
       <c r="B239" s="1">
-        <v>3311</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
-        <v>47.752132414999998</v>
+        <v>47.752132412999998</v>
       </c>
       <c r="B240" s="1">
-        <v>3326</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
-        <v>47.909695806999999</v>
+        <v>47.909695804999998</v>
       </c>
       <c r="B241" s="1">
-        <v>3343</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
-        <v>48.067259198999999</v>
+        <v>48.067259196999998</v>
       </c>
       <c r="B242" s="1">
-        <v>3481</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
-        <v>48.224822590999999</v>
+        <v>48.224822588999999</v>
       </c>
       <c r="B243" s="1">
-        <v>3537</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
-        <v>48.382385982999999</v>
+        <v>48.382385980999999</v>
       </c>
       <c r="B244" s="1">
-        <v>3455</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
-        <v>48.539949374999999</v>
+        <v>48.539949372999999</v>
       </c>
       <c r="B245" s="1">
-        <v>3596</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
-        <v>48.697512766999999</v>
+        <v>48.697512764999999</v>
       </c>
       <c r="B246" s="1">
-        <v>4325</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
-        <v>48.855076158999999</v>
+        <v>48.855076158000003</v>
       </c>
       <c r="B247" s="1">
-        <v>5397</v>
+        <v>4783</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
-        <v>49.012639552000003</v>
+        <v>49.012639550000003</v>
       </c>
       <c r="B248" s="1">
-        <v>4827</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
-        <v>49.170202944000003</v>
+        <v>49.170202942000003</v>
       </c>
       <c r="B249" s="1">
-        <v>3809</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
-        <v>49.327766336000003</v>
+        <v>49.327766334000003</v>
       </c>
       <c r="B250" s="1">
-        <v>3659</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
-        <v>49.485329728000004</v>
+        <v>49.485329726000003</v>
       </c>
       <c r="B251" s="1">
-        <v>3546</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
-        <v>49.642893119999997</v>
+        <v>49.642893118000003</v>
       </c>
       <c r="B252" s="1">
-        <v>3521</v>
+        <v>3479</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>49.800456509999997</v>
+      </c>
+      <c r="B253" s="1">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>49.958019901999997</v>
+      </c>
+      <c r="B254" s="1">
+        <v>3457</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>50.115583293999997</v>
+      </c>
+      <c r="B255" s="1">
+        <v>3462</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>50.273146685999997</v>
+      </c>
+      <c r="B256" s="1">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>50.430710079000001</v>
+      </c>
+      <c r="B257" s="1">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>50.588273471000001</v>
+      </c>
+      <c r="B258" s="1">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>50.745836863000001</v>
+      </c>
+      <c r="B259" s="1">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>50.903400255000001</v>
+      </c>
+      <c r="B260" s="1">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>51.060963647000001</v>
+      </c>
+      <c r="B261" s="1">
+        <v>3459</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>51.218527039000001</v>
+      </c>
+      <c r="B262" s="1">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>51.376090431000002</v>
+      </c>
+      <c r="B263" s="1">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>51.533653823000002</v>
+      </c>
+      <c r="B264" s="1">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>51.691217215000002</v>
+      </c>
+      <c r="B265" s="1">
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>51.848780607000002</v>
+      </c>
+      <c r="B266" s="1">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>52.006343999999999</v>
+      </c>
+      <c r="B267" s="1">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>52.163907391999999</v>
+      </c>
+      <c r="B268" s="1">
+        <v>3509</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>52.321470783999999</v>
+      </c>
+      <c r="B269" s="1">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>52.479034175999999</v>
+      </c>
+      <c r="B270" s="1">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>52.636597567999999</v>
+      </c>
+      <c r="B271" s="1">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>52.794160959999999</v>
+      </c>
+      <c r="B272" s="1">
+        <v>3427</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>52.951724351999999</v>
+      </c>
+      <c r="B273" s="1">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>53.109287744</v>
+      </c>
+      <c r="B274" s="1">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>53.266851136</v>
+      </c>
+      <c r="B275" s="1">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>53.424414529000003</v>
+      </c>
+      <c r="B276" s="1">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>53.581977920999996</v>
+      </c>
+      <c r="B277" s="1">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>53.739541312999997</v>
+      </c>
+      <c r="B278" s="1">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>53.897104704999997</v>
+      </c>
+      <c r="B279" s="1">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>54.054668096999997</v>
+      </c>
+      <c r="B280" s="1">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>54.212231488999997</v>
+      </c>
+      <c r="B281" s="1">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>54.369794880999997</v>
+      </c>
+      <c r="B282" s="1">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>54.527358272999997</v>
+      </c>
+      <c r="B283" s="1">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>54.684921664999997</v>
+      </c>
+      <c r="B284" s="1">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>54.842485056999998</v>
+      </c>
+      <c r="B285" s="1">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>55.000048450000001</v>
+      </c>
+      <c r="B286" s="1">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>55.157611842000001</v>
+      </c>
+      <c r="B287" s="1">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>55.315175234000002</v>
+      </c>
+      <c r="B288" s="1">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>55.472738626000002</v>
+      </c>
+      <c r="B289" s="1">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>55.630302018000002</v>
+      </c>
+      <c r="B290" s="1">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>55.787865410000002</v>
+      </c>
+      <c r="B291" s="1">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>55.945428802000002</v>
+      </c>
+      <c r="B292" s="1">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>56.102992194000002</v>
+      </c>
+      <c r="B293" s="1">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>56.260555586000002</v>
+      </c>
+      <c r="B294" s="1">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>56.418118978000003</v>
+      </c>
+      <c r="B295" s="1">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>56.575682370999999</v>
+      </c>
+      <c r="B296" s="1">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>56.733245762999999</v>
+      </c>
+      <c r="B297" s="1">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>56.890809154999999</v>
+      </c>
+      <c r="B298" s="1">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>57.048372547</v>
+      </c>
+      <c r="B299" s="1">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>57.205935939</v>
+      </c>
+      <c r="B300" s="1">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>57.363499331</v>
+      </c>
+      <c r="B301" s="1">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>57.521062723</v>
+      </c>
+      <c r="B302" s="1">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>57.678626115</v>
+      </c>
+      <c r="B303" s="1">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>57.836189507</v>
+      </c>
+      <c r="B304" s="1">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>57.993752899999997</v>
+      </c>
+      <c r="B305" s="1">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>58.151316291999997</v>
+      </c>
+      <c r="B306" s="1">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>58.308879683999997</v>
+      </c>
+      <c r="B307" s="1">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>58.466443075999997</v>
+      </c>
+      <c r="B308" s="1">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>58.624006467999997</v>
+      </c>
+      <c r="B309" s="1">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>58.781569859999998</v>
+      </c>
+      <c r="B310" s="1">
+        <v>5488</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <v>58.939133251999998</v>
+      </c>
+      <c r="B311" s="1">
+        <v>5845</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>59.096696643999998</v>
+      </c>
+      <c r="B312" s="1">
+        <v>5205</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <v>59.254260035999998</v>
+      </c>
+      <c r="B313" s="1">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <v>59.411823427999998</v>
+      </c>
+      <c r="B314" s="1">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>59.569386821000002</v>
+      </c>
+      <c r="B315" s="1">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>59.726950213000002</v>
+      </c>
+      <c r="B316" s="1">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="1">
+        <v>59.884513605000002</v>
+      </c>
+      <c r="B317" s="1">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="1">
+        <v>60.042076997000002</v>
+      </c>
+      <c r="B318" s="1">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="1">
+        <v>60.199640389000002</v>
+      </c>
+      <c r="B319" s="1">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="1">
+        <v>60.357203781000003</v>
+      </c>
+      <c r="B320" s="1">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="1">
+        <v>60.514767173000003</v>
+      </c>
+      <c r="B321" s="1">
+        <v>3747</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="1">
+        <v>60.672330565000003</v>
+      </c>
+      <c r="B322" s="1">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="1">
+        <v>60.829893957000003</v>
+      </c>
+      <c r="B323" s="1">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="1">
+        <v>60.987457349000003</v>
+      </c>
+      <c r="B324" s="1">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="1">
+        <v>61.145020742</v>
+      </c>
+      <c r="B325" s="1">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="1">
+        <v>61.302584134</v>
+      </c>
+      <c r="B326" s="1">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="1">
+        <v>61.460147526</v>
+      </c>
+      <c r="B327" s="1">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="1">
+        <v>61.617710918</v>
+      </c>
+      <c r="B328" s="1">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="1">
+        <v>61.77527431</v>
+      </c>
+      <c r="B329" s="1">
+        <v>3838</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>